--- a/analytics/excel/pl_Excel_report.xlsx
+++ b/analytics/excel/pl_Excel_report.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{9E0B8132-2D03-448E-A4A0-0A94058A5023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{E121E948-16AF-4D5D-BF17-4257D3C5D354}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{E121E948-16AF-4D5D-BF17-4257D3C5D354}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="14" r:id="rId1"/>
@@ -21,8 +21,8 @@
     <sheet name="Refresh" sheetId="10" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_pl_Excel_report.xlsxPlayers1" hidden="1">Players[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_pl_Excel_report1.xlsxFixtures1" hidden="1">Fixtures[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_pl_Excel_report.xlsxPlayers" hidden="1">Players[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_pl_Excel_report1.xlsxFixtures" hidden="1">Fixtures[]</definedName>
     <definedName name="ExternalData_2" localSheetId="4" hidden="1">Data!$A$1:$U$244</definedName>
     <definedName name="ExternalData_3" localSheetId="4" hidden="1">Data!$A$249:$F$909</definedName>
     <definedName name="ExternalData_3" localSheetId="5" hidden="1">'Refresh'!$A$1:$F$2</definedName>
@@ -30,8 +30,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="29" r:id="rId7"/>
-    <pivotCache cacheId="32" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="1" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
@@ -135,7 +135,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Fixtures 1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_pl_Excel_report1.xlsxFixtures1"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_pl_Excel_report1.xlsxFixtures"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -144,7 +144,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Players 1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_pl_Excel_report.xlsxPlayers1"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_pl_Excel_report.xlsxPlayers"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="2">
     <metadataType name="XLMDX" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
@@ -2320,7 +2320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2373,81 +2373,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="37">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2557,6 +2487,75 @@
           <bgColor rgb="FFDBECD0"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3617,10 +3616,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="admin" refreshedDate="46293.00885150463" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{0821162C-55F5-4F2B-94F5-F1130D8C5887}">
   <cacheSource type="external" connectionId="7"/>
@@ -4236,7 +4231,196 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28EB6D97-6CF4-4046-9202-0F4A6D2C6BC7}" name="PivotTable2" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E97AB150-9DC4-4A22-BFC8-0D7C75CCBB0F}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="27">
+  <location ref="A14:D24" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="6">
+    <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+    <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="10">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="2"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="0" hier="19" name="[Players].[position_short].[All]" cap="All"/>
+  </pageFields>
+  <dataFields count="3">
+    <dataField name="Points" fld="2" baseField="0" baseItem="0"/>
+    <dataField name="Price" fld="3" subtotal="max" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Avg pts/£m" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <pivotHierarchies count="65">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Points"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Price"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Avg pts/£m"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="count" id="1" iMeasureHier="59">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="10" filterVal="10"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="13"/>
+  </rowHierarchiesUsage>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="-2"/>
+  </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings>
+        <x15:activeTabTopLevelEntity name="[Players]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{28EB6D97-6CF4-4046-9202-0F4A6D2C6BC7}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A5:D9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -4431,195 +4615,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E97AB150-9DC4-4A22-BFC8-0D7C75CCBB0F}" name="PivotTable3" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="27">
-  <location ref="A14:D24" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="6">
-    <pivotField axis="axisPage" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-    <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="10">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="2"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="10">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="0" hier="19" name="[Players].[position_short].[All]" cap="All"/>
-  </pageFields>
-  <dataFields count="3">
-    <dataField name="Points" fld="2" baseField="0" baseItem="0"/>
-    <dataField name="Price" fld="3" subtotal="max" baseField="0" baseItem="0" numFmtId="165"/>
-    <dataField name="Avg pts/£m" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <pivotHierarchies count="65">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Points"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Price"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Avg pts/£m"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="1" type="count" id="1" iMeasureHier="59">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="10" filterVal="10"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="13"/>
-  </rowHierarchiesUsage>
-  <colHierarchiesUsage count="1">
-    <colHierarchyUsage hierarchyUsage="-2"/>
-  </colHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings>
-        <x15:activeTabTopLevelEntity name="[Players]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_2" backgroundRefresh="0" connectionId="1" xr16:uid="{FDBF5EF2-A3F8-41F9-B7BF-9483AE27891F}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="22">
@@ -4734,26 +4729,26 @@
   </sortState>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{3BC6AC42-036E-4533-BE3B-AC10CBB0D592}" uniqueName="1" name="player_id" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{723556B2-A75C-4412-B342-27168EBE000B}" uniqueName="2" name="web_name" queryTableFieldId="2" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{C4731C3F-6491-4CFF-A37B-F989AE1E3E89}" uniqueName="3" name="full_name" queryTableFieldId="3" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{723556B2-A75C-4412-B342-27168EBE000B}" uniqueName="2" name="web_name" queryTableFieldId="2" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{C4731C3F-6491-4CFF-A37B-F989AE1E3E89}" uniqueName="3" name="full_name" queryTableFieldId="3" dataDxfId="35"/>
     <tableColumn id="4" xr3:uid="{6A6A7C39-D002-4DBB-A4A4-EEBD43A1BB72}" uniqueName="4" name="price_m" queryTableFieldId="4"/>
     <tableColumn id="20" xr3:uid="{247234BF-45F5-4C57-910E-8F29A7661F76}" uniqueName="20" name="Column1" queryTableFieldId="21"/>
     <tableColumn id="21" xr3:uid="{9877304F-B224-4FF9-AD02-2388722D0AF6}" uniqueName="21" name="Column2" queryTableFieldId="20"/>
     <tableColumn id="5" xr3:uid="{E512F3C8-4B68-4EDB-BC2A-73EB537B5BEE}" uniqueName="5" name="selected_by_percent" queryTableFieldId="5"/>
-    <tableColumn id="6" xr3:uid="{CB6BA7D4-6B75-4622-B277-9314C1853A66}" uniqueName="6" name="status" queryTableFieldId="6" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{C6A5B11A-C39D-4EFE-AB7D-10CBDF5CDC8C}" uniqueName="7" name="team_name" queryTableFieldId="7" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{36FE0214-D386-4810-88F8-63F41A16FCF3}" uniqueName="8" name="position_short" queryTableFieldId="8" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{CB1E0731-5C5C-46A4-A6F6-66608404B32F}" uniqueName="9" name="position_name" queryTableFieldId="9" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{06751EFD-9706-4BA2-810E-50330E5FB7E8}" uniqueName="10" name="fixtures" queryTableFieldId="10" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{F58372D5-D488-4846-90E5-6DB715035C3C}" uniqueName="11" name="appearances" queryTableFieldId="11" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{CB6BA7D4-6B75-4622-B277-9314C1853A66}" uniqueName="6" name="status" queryTableFieldId="6" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{C6A5B11A-C39D-4EFE-AB7D-10CBDF5CDC8C}" uniqueName="7" name="team_name" queryTableFieldId="7" dataDxfId="33"/>
+    <tableColumn id="8" xr3:uid="{36FE0214-D386-4810-88F8-63F41A16FCF3}" uniqueName="8" name="position_short" queryTableFieldId="8" dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{CB1E0731-5C5C-46A4-A6F6-66608404B32F}" uniqueName="9" name="position_name" queryTableFieldId="9" dataDxfId="31"/>
+    <tableColumn id="10" xr3:uid="{06751EFD-9706-4BA2-810E-50330E5FB7E8}" uniqueName="10" name="fixtures" queryTableFieldId="10" dataDxfId="30"/>
+    <tableColumn id="11" xr3:uid="{F58372D5-D488-4846-90E5-6DB715035C3C}" uniqueName="11" name="appearances" queryTableFieldId="11" dataDxfId="29"/>
     <tableColumn id="12" xr3:uid="{A289A82B-9745-4E2B-BAFE-1C7B24F910B1}" uniqueName="12" name="minutes" queryTableFieldId="12"/>
     <tableColumn id="13" xr3:uid="{6F00784E-3561-442A-88D9-15F5FDC1FDF7}" uniqueName="13" name="points" queryTableFieldId="13"/>
-    <tableColumn id="14" xr3:uid="{6142D92C-B225-4537-B048-2480FB33C094}" uniqueName="14" name="goals" queryTableFieldId="14" dataDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{0FF6CD34-C407-47D7-9DAB-6DFD1A287843}" uniqueName="15" name="assists" queryTableFieldId="15" dataDxfId="13"/>
-    <tableColumn id="16" xr3:uid="{77D85C73-E58A-4336-B064-258CEC7DFB2D}" uniqueName="16" name="clean_sheets" queryTableFieldId="16" dataDxfId="12"/>
-    <tableColumn id="17" xr3:uid="{F38FFC9F-4753-49EB-AA87-3942D81984E9}" uniqueName="17" name="bonus" queryTableFieldId="17" dataDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{6142D92C-B225-4537-B048-2480FB33C094}" uniqueName="14" name="goals" queryTableFieldId="14" dataDxfId="28"/>
+    <tableColumn id="15" xr3:uid="{0FF6CD34-C407-47D7-9DAB-6DFD1A287843}" uniqueName="15" name="assists" queryTableFieldId="15" dataDxfId="27"/>
+    <tableColumn id="16" xr3:uid="{77D85C73-E58A-4336-B064-258CEC7DFB2D}" uniqueName="16" name="clean_sheets" queryTableFieldId="16" dataDxfId="26"/>
+    <tableColumn id="17" xr3:uid="{F38FFC9F-4753-49EB-AA87-3942D81984E9}" uniqueName="17" name="bonus" queryTableFieldId="17" dataDxfId="25"/>
     <tableColumn id="18" xr3:uid="{23E5C6E0-636D-4246-BC5F-E36F4A3BF4F0}" uniqueName="18" name="points_per_million" queryTableFieldId="18"/>
-    <tableColumn id="19" xr3:uid="{331759ED-E96C-4B3E-AA26-E303C1A21362}" uniqueName="19" name="price_band" queryTableFieldId="19" dataDxfId="10"/>
+    <tableColumn id="19" xr3:uid="{331759ED-E96C-4B3E-AA26-E303C1A21362}" uniqueName="19" name="price_band" queryTableFieldId="19" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4763,12 +4758,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{FADF3108-5EB4-47BF-86B4-4AD56AE906DF}" name="Fixtures" displayName="Fixtures" ref="A249:F909" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A249:F909" xr:uid="{FADF3108-5EB4-47BF-86B4-4AD56AE906DF}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{64DFFADF-04CF-4B78-9700-82C8D98681F0}" uniqueName="1" name="team_name" queryTableFieldId="1" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{68FAFAD1-B43A-4A33-852E-4966C6E7485B}" uniqueName="5" name="opponent_name" queryTableFieldId="5" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{64DFFADF-04CF-4B78-9700-82C8D98681F0}" uniqueName="1" name="team_name" queryTableFieldId="1" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{68FAFAD1-B43A-4A33-852E-4966C6E7485B}" uniqueName="5" name="opponent_name" queryTableFieldId="5" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{AC054F20-50A2-4908-9E73-1515B412AA18}" uniqueName="2" name="gameweek_id" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{C6A6C03D-16D9-4FEB-9AE9-2AA155053EEF}" uniqueName="3" name="difficulty" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{277416E4-A86E-41B7-BFD9-463831613956}" uniqueName="4" name="venue" queryTableFieldId="4" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{9EF7284D-B9D1-41CE-BBAD-2F8B5F7A2A00}" uniqueName="6" name="fixture_label" queryTableFieldId="6" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{277416E4-A86E-41B7-BFD9-463831613956}" uniqueName="4" name="venue" queryTableFieldId="4" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{9EF7284D-B9D1-41CE-BBAD-2F8B5F7A2A00}" uniqueName="6" name="fixture_label" queryTableFieldId="6" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4778,12 +4773,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{47260952-CE43-4FAC-B2ED-CFAEB7CA5DC0}" name="Refresh" displayName="Refresh" ref="A1:F2" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:F2" xr:uid="{47260952-CE43-4FAC-B2ED-CFAEB7CA5DC0}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{D3B6D04D-1A32-44BA-8AB8-1038BCD1DF19}" uniqueName="1" name="refreshed_at" queryTableFieldId="1" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{DFF7A08D-D476-4485-AF3B-222980A7BC4F}" uniqueName="2" name="total_matches" queryTableFieldId="2" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{F196E000-A4BB-4509-88D9-1536E84E988F}" uniqueName="3" name="live_matches" queryTableFieldId="3" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{87A53F3C-005B-44F8-B348-EACEA7A301EE}" uniqueName="4" name="player_fixture_rows" queryTableFieldId="4" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{2C13A3AC-3F1F-4BA0-BC89-85FAE728F205}" uniqueName="5" name="latest_gameweek" queryTableFieldId="5" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{428E47EE-64CD-44F9-9783-1D5B3915E33D}" uniqueName="6" name="latest_match_date" queryTableFieldId="6" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D3B6D04D-1A32-44BA-8AB8-1038BCD1DF19}" uniqueName="1" name="refreshed_at" queryTableFieldId="1" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{DFF7A08D-D476-4485-AF3B-222980A7BC4F}" uniqueName="2" name="total_matches" queryTableFieldId="2" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{F196E000-A4BB-4509-88D9-1536E84E988F}" uniqueName="3" name="live_matches" queryTableFieldId="3" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{87A53F3C-005B-44F8-B348-EACEA7A301EE}" uniqueName="4" name="player_fixture_rows" queryTableFieldId="4" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{2C13A3AC-3F1F-4BA0-BC89-85FAE728F205}" uniqueName="5" name="latest_gameweek" queryTableFieldId="5" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{428E47EE-64CD-44F9-9783-1D5B3915E33D}" uniqueName="6" name="latest_match_date" queryTableFieldId="6" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5357,7 +5352,7 @@
       <c r="A15" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15">
         <v>42</v>
       </c>
       <c r="C15" s="5">
@@ -5379,7 +5374,7 @@
       <c r="A16" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16">
         <v>47</v>
       </c>
       <c r="C16" s="5">
@@ -5402,7 +5397,7 @@
       <c r="A17" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17">
         <v>38</v>
       </c>
       <c r="C17" s="5">
@@ -5424,7 +5419,7 @@
       <c r="A18" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="28">
+      <c r="B18">
         <v>34</v>
       </c>
       <c r="C18" s="5">
@@ -5446,7 +5441,7 @@
       <c r="A19" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19">
         <v>43</v>
       </c>
       <c r="C19" s="5">
@@ -5468,7 +5463,7 @@
       <c r="A20" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20">
         <v>37</v>
       </c>
       <c r="C20" s="5">
@@ -5490,7 +5485,7 @@
       <c r="A21" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21">
         <v>27</v>
       </c>
       <c r="C21" s="5">
@@ -5512,7 +5507,7 @@
       <c r="A22" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22">
         <v>32</v>
       </c>
       <c r="C22" s="5">
@@ -5534,7 +5529,7 @@
       <c r="A23" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23">
         <v>26</v>
       </c>
       <c r="C23" s="5">
@@ -5556,7 +5551,7 @@
       <c r="A24" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24">
         <v>39</v>
       </c>
       <c r="C24" s="5">
@@ -6286,36 +6281,36 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B28:F47">
-    <cfRule type="expression" dxfId="36" priority="11">
+    <cfRule type="expression" dxfId="13" priority="11">
       <formula>VALUE(RIGHT(B28,1))=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="12">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>VALUE(RIGHT(B28,1))=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="13">
+    <cfRule type="expression" dxfId="11" priority="13">
       <formula>VALUE(RIGHT(B28,1))=5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="14">
+    <cfRule type="expression" dxfId="10" priority="14">
       <formula>VALUE(RIGHT(B28,1))=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="15">
+    <cfRule type="expression" dxfId="9" priority="15">
       <formula>VALUE(RIGHT(B28,1))=4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:F24 H5:H7">
-    <cfRule type="expression" dxfId="31" priority="6">
+  <conditionalFormatting sqref="H5:H7 B5:F24">
+    <cfRule type="expression" dxfId="8" priority="6">
       <formula>VALUE(RIGHT(B5,1))=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="7">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>VALUE(RIGHT(B5,1))=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="8">
+    <cfRule type="expression" dxfId="6" priority="8">
       <formula>VALUE(RIGHT(B5,1))=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="9">
+    <cfRule type="expression" dxfId="5" priority="9">
       <formula>VALUE(RIGHT(B5,1))=4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="10">
+    <cfRule type="expression" dxfId="4" priority="10">
       <formula>VALUE(RIGHT(B5,1))=5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6838,20 +6833,6 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J31">
-    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="Avoid">
-      <formula>NOT(ISERROR(SEARCH("Avoid",J2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="Strong">
-      <formula>NOT(ISERROR(SEARCH("Strong",J2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="&quot;Avoid&quot;">
-      <formula>NOT(ISERROR(SEARCH("""Avoid""",J2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="6" operator="containsText" text="&quot;Strong&quot;">
-      <formula>NOT(ISERROR(SEARCH("""Strong""",J2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="I2:I31">
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -6862,6 +6843,20 @@
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J31">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Avoid">
+      <formula>NOT(ISERROR(SEARCH("Avoid",J2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Strong">
+      <formula>NOT(ISERROR(SEARCH("Strong",J2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="&quot;Avoid&quot;">
+      <formula>NOT(ISERROR(SEARCH("""Avoid""",J2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="&quot;Strong&quot;">
+      <formula>NOT(ISERROR(SEARCH("""Strong""",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
